--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,12 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R3" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -878,19 +873,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -934,12 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R4" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +980,9 @@
           <t>1997-07-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1997-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R5" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1091,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R6" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1248,19 +1198,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1304,12 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R7" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1374,19 +1309,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1430,12 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R8" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1500,19 +1420,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1556,12 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R9" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1626,19 +1531,9 @@
           <t>1995-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1995-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1682,12 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R10" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1752,19 +1642,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1808,12 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101877</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566898.7409364481</v>
+        <v>566899</v>
       </c>
       <c r="R11" t="n">
-        <v>6356643.678009531</v>
+        <v>6356644</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1878,19 +1753,9 @@
           <t>1995-07-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105806</v>
+        <v>105815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104532</v>
+        <v>104541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101853</v>
+        <v>101859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101877</v>
+        <v>101883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105815</v>
+        <v>105820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104541</v>
+        <v>104544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101883</v>
+        <v>101884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105820</v>
+        <v>105848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104544</v>
+        <v>104571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101860</v>
+        <v>101887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101884</v>
+        <v>101911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105848</v>
+        <v>105854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104571</v>
+        <v>104577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101887</v>
+        <v>101893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101911</v>
+        <v>101917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105854</v>
+        <v>105861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104577</v>
+        <v>104584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101893</v>
+        <v>101900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101917</v>
+        <v>101924</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104584</v>
+        <v>104588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101900</v>
+        <v>101904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101924</v>
+        <v>101928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105865</v>
+        <v>105872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104588</v>
+        <v>104595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101904</v>
+        <v>101911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101928</v>
+        <v>101935</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105875</v>
+        <v>105880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98648</v>
+        <v>98653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104598</v>
+        <v>104603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101914</v>
+        <v>101919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101938</v>
+        <v>101943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105880</v>
+        <v>105888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98653</v>
+        <v>98661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104603</v>
+        <v>104611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101919</v>
+        <v>101927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101943</v>
+        <v>101951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>73982296</v>
       </c>
       <c r="B3" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>74440461</v>
       </c>
       <c r="B4" t="n">
-        <v>105888</v>
+        <v>105898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74467877</v>
       </c>
       <c r="B5" t="n">
-        <v>98661</v>
+        <v>98671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74463492</v>
       </c>
       <c r="B6" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>74769929</v>
       </c>
       <c r="B7" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>74843841</v>
       </c>
       <c r="B8" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>75060367</v>
       </c>
       <c r="B9" t="n">
-        <v>104611</v>
+        <v>104621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>75155546</v>
       </c>
       <c r="B10" t="n">
-        <v>101927</v>
+        <v>101937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>75157904</v>
       </c>
       <c r="B11" t="n">
-        <v>101951</v>
+        <v>101961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54470112</v>
+        <v>75060367</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>1560</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +703,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallebosjön, SO, Sm</t>
+          <t>Hagen 650 m SV. Fallebosjön S, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566787.967872949</v>
+        <v>566899</v>
       </c>
       <c r="R2" t="n">
-        <v>6356705.547902201</v>
+        <v>6356644</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Thesium alpinum. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,60 +764,60 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskogsbryn</t>
+          <t>Torräng</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Via Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73982296</v>
+        <v>74467867</v>
       </c>
       <c r="B3" t="n">
-        <v>109264</v>
+        <v>99120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
+          <t>Fallebosjön, sydost, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -870,17 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>1999-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>1999-06-19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Hypochoeris maculata. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Gymnadenia conopsea. LEG: Åke Rühling. KOM: 12 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Torräng</t>
+          <t>Null</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,34 +897,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74440461</v>
+        <v>74769929</v>
       </c>
       <c r="B4" t="n">
-        <v>105898</v>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221447</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fallebosjön sydost, Sm</t>
+          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -977,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1997-07-11</t>
+          <t>1995-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1997-07-11</t>
+          <t>1995-07-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Gentianella campestris. LEG: Åke Rühling. KOM: 30 ex</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Platanthera bifolia. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Torräng</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,48 +1008,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74467877</v>
+        <v>54470112</v>
       </c>
       <c r="B5" t="n">
-        <v>98671</v>
+        <v>109815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
+          <t>Fallebosjön, SO, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566899</v>
+        <v>566788</v>
       </c>
       <c r="R5" t="n">
-        <v>6356644</v>
+        <v>6356706</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,19 +1080,19 @@
           <t>Kristdala</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Arkiv-Hf-Osk-0453</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Gymnadenia conopsea. LEG: Åke Rühling</t>
+          <t>2015-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,32 +1106,32 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Torräng</t>
+          <t>Barrskogsbryn</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74463492</v>
+        <v>73982296</v>
       </c>
       <c r="B6" t="n">
-        <v>104150</v>
+        <v>109814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,19 +1139,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224416</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,7 +1203,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Helianthemum nummularium ssp. nummularium. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Hypochoeris maculata. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74769929</v>
+        <v>74843841</v>
       </c>
       <c r="B7" t="n">
-        <v>98703</v>
+        <v>106155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>221141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1316,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Platanthera bifolia. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Primula veris. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,32 +1350,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74843841</v>
+        <v>75155546</v>
       </c>
       <c r="B8" t="n">
-        <v>105644</v>
+        <v>102418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1425,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Primula veris. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Trifolium aureum. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75060367</v>
+        <v>75157904</v>
       </c>
       <c r="B9" t="n">
-        <v>104621</v>
+        <v>102442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,16 +1472,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1560</v>
+        <v>221333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelört</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thesium alpinum</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1494,7 +1492,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagen 650 m SV. Fallebosjön S, Sm</t>
+          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1528,17 +1526,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
+          <t>1995-07-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1995-12-31</t>
+          <t>1995-07-11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Thesium alpinum. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Trifolium montanum. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,38 +1572,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75155546</v>
+        <v>74440457</v>
       </c>
       <c r="B10" t="n">
-        <v>101937</v>
+        <v>106413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221317</v>
+        <v>221447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Pollich</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
+          <t>Fallebosjön sydost, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1639,17 +1633,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>1970-12-31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Trifolium aureum. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Gentianella campestris. LEG: Mårten Aronsson. KOM: 30-40 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,7 +1657,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Torräng</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75157904</v>
+        <v>74782395</v>
       </c>
       <c r="B11" t="n">
-        <v>101961</v>
+        <v>102559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,16 +1690,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221333</v>
+        <v>222133</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1760,7 +1754,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Trifolium montanum. LEG: Åke Rühling</t>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Polygala vulgaris. LEG: Åke Rühling</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,6 +1783,113 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74463492</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>650 m SV Hagen, syd Fallebosjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566899</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6356644</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1995-07-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1995-07-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6G1d 3034. SOM: Helianthemum nummularium ssp. nummularium. LEG: Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Torräng</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 10887-2025 artfynd.xlsx
+++ b/artfynd/A 10887-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75060367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74467867</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74769929</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54470112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74843841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75155546</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75157904</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1676,6 +1721,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74440457</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782395</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,8 +1949,26 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74463492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>